--- a/Agile_epic_User_stories.xlsx
+++ b/Agile_epic_User_stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BA-Harsha\OpenCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A29ADF-7984-4875-B846-2FF0569E539B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C37117F9-08BE-4728-B168-ADE0D015007C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{5E9EE2BA-46DA-4B75-A8EF-293F14D1EFC7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="43">
   <si>
     <t>Column1</t>
   </si>
@@ -174,7 +174,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,6 +209,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -218,7 +226,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -297,33 +305,6 @@
       <top/>
       <bottom style="medium">
         <color rgb="FFC4C7C5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFC4C7C5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -350,22 +331,27 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color rgb="FFC4C7C5"/>
-      </top>
-      <bottom/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -375,54 +361,58 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -457,7 +447,9 @@
         </right>
         <top/>
         <bottom/>
-        <vertical/>
+        <vertical style="medium">
+          <color indexed="64"/>
+        </vertical>
         <horizontal/>
       </border>
     </dxf>
@@ -481,14 +473,16 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
-          <color rgb="FFC4C7C5"/>
+          <color indexed="64"/>
         </left>
         <right style="medium">
-          <color rgb="FFC4C7C5"/>
+          <color indexed="64"/>
         </right>
         <top/>
         <bottom/>
-        <vertical/>
+        <vertical style="medium">
+          <color indexed="64"/>
+        </vertical>
         <horizontal/>
       </border>
     </dxf>
@@ -500,7 +494,9 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
-        <vertical/>
+        <vertical style="medium">
+          <color indexed="64"/>
+        </vertical>
       </border>
     </dxf>
     <dxf>
@@ -523,14 +519,16 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
-          <color rgb="FFC4C7C5"/>
+          <color indexed="64"/>
         </left>
         <right style="medium">
-          <color rgb="FFC4C7C5"/>
+          <color indexed="64"/>
         </right>
         <top/>
         <bottom/>
-        <vertical/>
+        <vertical style="medium">
+          <color indexed="64"/>
+        </vertical>
         <horizontal/>
       </border>
     </dxf>
@@ -561,7 +559,9 @@
         </right>
         <top/>
         <bottom/>
-        <vertical/>
+        <vertical style="medium">
+          <color indexed="64"/>
+        </vertical>
         <horizontal/>
       </border>
     </dxf>
@@ -592,8 +592,52 @@
         </right>
         <top/>
         <bottom/>
-        <vertical/>
+        <vertical style="medium">
+          <color indexed="64"/>
+        </vertical>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -625,48 +669,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color rgb="FFC4C7C5"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFC4C7C5"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -692,8 +694,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C10AE4AE-43EA-445C-9093-902BBC7C2B17}" name="Table3" displayName="Table3" ref="A10:F30" totalsRowShown="0" headerRowDxfId="6" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="9">
-  <autoFilter ref="A10:F30" xr:uid="{C10AE4AE-43EA-445C-9093-902BBC7C2B17}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C10AE4AE-43EA-445C-9093-902BBC7C2B17}" name="Table3" displayName="Table3" ref="A10:F32" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6">
+  <autoFilter ref="A10:F32" xr:uid="{C10AE4AE-43EA-445C-9093-902BBC7C2B17}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{FB18DC73-62F4-4F4F-A470-372F42832BBC}" name="Epic" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{FFDF7FB3-3F4C-4777-ABA3-E415C6DE68E8}" name="User Story ID" dataDxfId="4"/>
@@ -1023,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1CCE42F-5721-4A76-BC4E-40C8EB1B7681}">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
@@ -1082,262 +1084,306 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
-    </row>
     <row r="9" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="14"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
     </row>
     <row r="10" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="E10" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="0.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="13"/>
+    <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
     </row>
     <row r="13" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+    </row>
+    <row r="15" spans="1:6" ht="85.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="5" t="s">
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="11" t="s">
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+    </row>
+    <row r="16" spans="1:6" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+    </row>
+    <row r="17" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="17"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="19"/>
-    </row>
-    <row r="16" spans="1:6" ht="93.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="12" t="s">
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="18"/>
+      <c r="B18" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C18" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D18" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E18" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F18" s="22" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="5"/>
-    </row>
-    <row r="18" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="11" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+    </row>
+    <row r="20" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="5"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="5"/>
-    </row>
-    <row r="20" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="19"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11" t="s">
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+    </row>
+    <row r="22" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="19"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="10"/>
-      <c r="F20" s="11"/>
-    </row>
-    <row r="21" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="12"/>
-      <c r="B21" s="5" t="s">
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="18"/>
+      <c r="B23" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C23" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D23" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E23" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F23" s="22" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="5" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+    </row>
+    <row r="25" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="7"/>
-      <c r="F23" s="5"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="5"/>
-    </row>
-    <row r="25" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="19"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+    </row>
+    <row r="27" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="19"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E25" s="7"/>
-      <c r="F25" s="5"/>
-    </row>
-    <row r="26" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="12"/>
-      <c r="B26" s="13" t="s">
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="18"/>
+      <c r="B28" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C28" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D28" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E28" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="F26" s="13" t="s">
+      <c r="F28" s="22" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="5"/>
-    </row>
-    <row r="28" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="5" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+    </row>
+    <row r="30" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E28" s="7"/>
-      <c r="F28" s="5"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="5"/>
-    </row>
-    <row r="30" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="11" t="s">
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+    </row>
+    <row r="32" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E30" s="10"/>
-      <c r="F30" s="11"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="A23:A27"/>
+    <mergeCell ref="B23:B27"/>
+    <mergeCell ref="C23:C27"/>
+    <mergeCell ref="E23:E27"/>
+    <mergeCell ref="F23:F27"/>
+    <mergeCell ref="A28:A32"/>
+    <mergeCell ref="B28:B32"/>
+    <mergeCell ref="C28:C32"/>
+    <mergeCell ref="E28:E32"/>
+    <mergeCell ref="F28:F32"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="E13:E17"/>
+    <mergeCell ref="F13:F17"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="B18:B22"/>
+    <mergeCell ref="C18:C22"/>
+    <mergeCell ref="E18:E22"/>
+    <mergeCell ref="F18:F22"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">

--- a/Agile_epic_User_stories.xlsx
+++ b/Agile_epic_User_stories.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BA-Harsha\OpenCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C37117F9-08BE-4728-B168-ADE0D015007C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{3B25BBF2-42F4-43DB-9917-2BAE24843E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{5E9EE2BA-46DA-4B75-A8EF-293F14D1EFC7}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" activeTab="1" xr2:uid="{5E9EE2BA-46DA-4B75-A8EF-293F14D1EFC7}"/>
   </bookViews>
   <sheets>
     <sheet name="product backlog" sheetId="1" r:id="rId1"/>
+    <sheet name="sprint Planning" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="59">
   <si>
     <t>Column1</t>
   </si>
@@ -104,12 +106,6 @@
     <t>As a First-time visitor to the e-commerce website,</t>
   </si>
   <si>
-    <t>I want to register my account,</t>
-  </si>
-  <si>
-    <t>So that I can login to application.</t>
-  </si>
-  <si>
     <t>New</t>
   </si>
   <si>
@@ -168,13 +164,94 @@
   </si>
   <si>
     <t>User should able to search products and add them to cart.</t>
+  </si>
+  <si>
+    <t>As a First-time visitor to the e-commerce website,
+I want to register my account,
+So that I can login to application.</t>
+  </si>
+  <si>
+    <t>feature / Title</t>
+  </si>
+  <si>
+    <t>story points</t>
+  </si>
+  <si>
+    <t>Sprint</t>
+  </si>
+  <si>
+    <t>user story</t>
+  </si>
+  <si>
+    <t>Story User ID</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">OpenCart_Epic_001 :     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                For a new e-commerce website to launch, the highest Business Value will be when a new user is able to buy an item from the website.</t>
+    </r>
+  </si>
+  <si>
+    <t>new</t>
+  </si>
+  <si>
+    <t>login</t>
+  </si>
+  <si>
+    <t>logout</t>
+  </si>
+  <si>
+    <t>As a registered user,
+I want to login to the website,
+So that I can see my account details etc..</t>
+  </si>
+  <si>
+    <t>As a registered user,
+I want to logout from website,
+So that no one else can't access my account.</t>
+  </si>
+  <si>
+    <t>As a user,
+I want to be able to search items,
+So that I can add them to cart and do payment.</t>
+  </si>
+  <si>
+    <t>Story Points</t>
+  </si>
+  <si>
+    <t>Hours</t>
+  </si>
+  <si>
+    <t>1hour/day (depends on company)</t>
+  </si>
+  <si>
+    <t>0,1,2,3,5,8</t>
+  </si>
+  <si>
+    <t>fibbonaci series</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -217,16 +294,48 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor theme="0" tint="-0.34998626667073579"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -345,11 +454,88 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -388,9 +574,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -400,26 +583,224 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="15">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -447,9 +828,7 @@
         </right>
         <top/>
         <bottom/>
-        <vertical style="medium">
-          <color indexed="64"/>
-        </vertical>
+        <vertical/>
         <horizontal/>
       </border>
     </dxf>
@@ -480,55 +859,7 @@
         </right>
         <top/>
         <bottom/>
-        <vertical style="medium">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <vertical style="medium">
-          <color indexed="64"/>
-        </vertical>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="medium">
-          <color indexed="64"/>
-        </vertical>
+        <vertical/>
         <horizontal/>
       </border>
     </dxf>
@@ -559,9 +890,7 @@
         </right>
         <top/>
         <bottom/>
-        <vertical style="medium">
-          <color indexed="64"/>
-        </vertical>
+        <vertical/>
         <horizontal/>
       </border>
     </dxf>
@@ -592,26 +921,8 @@
         </right>
         <top/>
         <bottom/>
-        <vertical style="medium">
-          <color indexed="64"/>
-        </vertical>
+        <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color rgb="FFC4C7C5"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFC4C7C5"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -632,41 +943,24 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <border outline="0">
         <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
+          <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFC4C7C5"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top/>
-        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -694,17 +988,43 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C10AE4AE-43EA-445C-9093-902BBC7C2B17}" name="Table3" displayName="Table3" ref="A10:F32" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6">
-  <autoFilter ref="A10:F32" xr:uid="{C10AE4AE-43EA-445C-9093-902BBC7C2B17}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3264DA94-FA46-4CFD-82AF-B98C41D4028E}" name="Table2" displayName="Table2" ref="A10:F32" totalsRowShown="0" dataDxfId="8" tableBorderDxfId="14">
+  <autoFilter ref="A10:F32" xr:uid="{3264DA94-FA46-4CFD-82AF-B98C41D4028E}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{FB18DC73-62F4-4F4F-A470-372F42832BBC}" name="Epic" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{FFDF7FB3-3F4C-4777-ABA3-E415C6DE68E8}" name="User Story ID" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{E06F1725-2CB5-40CC-ABBC-5678BD0CE47D}" name="Feature/Title" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{D9F81C80-0D49-407C-AAC5-8CA75241A488}" name="User Story" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{F8CE7832-0F53-458E-81C7-4B438A714B48}" name="Status" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{102BE5BE-48F1-4391-820F-4687EED49A0A}" name="Acceptance Creteria" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{DDE5375D-53D2-4166-BAE6-B390F8574CDD}" name="Epic" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{862CEDB0-ADD3-4612-8B77-B5BF08C8DCD3}" name="User Story ID" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{EF5A6DCF-2565-44EB-B79B-7DDA8AC7D1A9}" name="Feature/Title" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{2B3A69F0-E6CC-425E-99FB-7034B3EC55B3}" name="User Story"/>
+    <tableColumn id="5" xr3:uid="{984D6B8B-C952-4E2A-9651-E1549C58C4B7}" name="Status" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{5B1D68AD-371D-4429-8EF4-14C5F6F39CAF}" name="Acceptance Creteria" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{FB1BF702-5509-4BA2-A0B8-4B64FBE77B27}" name="Table6" displayName="Table6" ref="A8:F12" totalsRowShown="0">
+  <autoFilter ref="A8:F12" xr:uid="{FB1BF702-5509-4BA2-A0B8-4B64FBE77B27}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{5838786A-E8B9-44E0-9C6C-3AC9F2EBFCE3}" name="Epic" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{A3192A69-239F-441F-9194-795FEEEEE2E2}" name="Story User ID" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{D6274389-32E0-44CA-8402-097BA09E22EA}" name="feature / Title" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{19776F6E-0E54-4EB9-AF0A-1EE4E6D7FDE5}" name="user story" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{F88720F6-90F2-48CB-A786-EB4DF7A34A30}" name="story points" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{F10FAB25-A110-4CB2-8CD7-88F85C81A1D2}" name="Sprint" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3A74D2A9-185F-4472-BB99-15386E0D5B1F}" name="Table7" displayName="Table7" ref="A15:B18" totalsRowShown="0">
+  <autoFilter ref="A15:B18" xr:uid="{3A74D2A9-185F-4472-BB99-15386E0D5B1F}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{DDCE6CCB-8D3F-46C8-A360-92CA0ABF2F48}" name="Story Points" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{C7075080-1827-4BE7-AE93-41FCA8742295}" name="Hours" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1028,12 +1348,12 @@
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.5703125" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" customWidth="1"/>
     <col min="2" max="2" width="24.85546875" customWidth="1"/>
     <col min="3" max="3" width="17.42578125" customWidth="1"/>
-    <col min="4" max="4" width="27.5703125" customWidth="1"/>
+    <col min="4" max="4" width="37.85546875" customWidth="1"/>
     <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="26.85546875" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1109,7 +1429,7 @@
         <v>15</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="0.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1126,264 +1446,249 @@
         <v>20</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>24</v>
+      <c r="E13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
       <c r="D14" s="3"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-    </row>
-    <row r="15" spans="1:6" ht="85.5" x14ac:dyDescent="0.25">
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
+      <c r="B15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="D15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="16"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7"/>
+      <c r="B18" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-    </row>
-    <row r="16" spans="1:6" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-    </row>
-    <row r="17" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="18"/>
-      <c r="B18" s="22" t="s">
+      <c r="F18" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="17"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="7"/>
+      <c r="B23" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18" s="22" t="s">
+      <c r="E23" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="17"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="7"/>
+      <c r="B28" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-    </row>
-    <row r="20" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-    </row>
-    <row r="22" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="19"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="18"/>
-      <c r="B23" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" s="22" t="s">
+      <c r="C28" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-    </row>
-    <row r="25" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-    </row>
-    <row r="27" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="19"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="18"/>
-      <c r="B28" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="C28" s="22" t="s">
+      <c r="E28" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E28" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="F28" s="22" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-    </row>
-    <row r="30" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="14"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="14"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-    </row>
-    <row r="32" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A23:A27"/>
-    <mergeCell ref="B23:B27"/>
-    <mergeCell ref="C23:C27"/>
-    <mergeCell ref="E23:E27"/>
-    <mergeCell ref="F23:F27"/>
-    <mergeCell ref="A28:A32"/>
-    <mergeCell ref="B28:B32"/>
-    <mergeCell ref="C28:C32"/>
-    <mergeCell ref="E28:E32"/>
-    <mergeCell ref="F28:F32"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="E13:E17"/>
-    <mergeCell ref="F13:F17"/>
-    <mergeCell ref="A18:A22"/>
-    <mergeCell ref="B18:B22"/>
-    <mergeCell ref="C18:C22"/>
-    <mergeCell ref="E18:E22"/>
-    <mergeCell ref="F18:F22"/>
-  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
@@ -1391,4 +1696,192 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{415AB877-52F8-4B59-A0D5-2873000E49A7}">
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="29.28515625" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" customWidth="1"/>
+    <col min="4" max="4" width="43.85546875" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="32">
+        <v>8</v>
+      </c>
+      <c r="F9" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="24"/>
+      <c r="B10" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="33">
+        <v>5</v>
+      </c>
+      <c r="F10" s="33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="24"/>
+      <c r="B11" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="32">
+        <v>3</v>
+      </c>
+      <c r="F11" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="25"/>
+      <c r="B12" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="34">
+        <v>5</v>
+      </c>
+      <c r="F12" s="34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="35">
+        <v>1</v>
+      </c>
+      <c r="B16" s="36" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="37"/>
+      <c r="B17" s="38"/>
+    </row>
+    <row r="18" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="40" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="92.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:2" ht="48.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:2" ht="52.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>